--- a/artfynd/A 14591-2026 artfynd.xlsx
+++ b/artfynd/A 14591-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132820733</v>
+        <v>132820663</v>
       </c>
       <c r="B2" t="n">
-        <v>57955</v>
+        <v>91970</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -756,17 +755,13 @@
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>hack i basen på gran</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,41 +780,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132820663</v>
+        <v>132820733</v>
       </c>
       <c r="B3" t="n">
-        <v>91916</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -865,13 +861,17 @@
           <t>2026-04-10</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>hack i basen på gran</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
